--- a/analysis/tables/pythia-6.9b.xlsx
+++ b/analysis/tables/pythia-6.9b.xlsx
@@ -536,27 +536,27 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.8915083820869502</v>
+        <v>0.6478294243165168</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1629372939571492</v>
+        <v>-0.06784306653454114</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>y = 0.892x - 0.163</t>
+          <t>y = 0.648x - 0.068</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.8554446488756218</v>
+        <v>0.8554446488756207</v>
       </c>
       <c r="H3" t="n">
-        <v>0.07373002956964288</v>
+        <v>0.07373002956964289</v>
       </c>
       <c r="I3" t="n">
-        <v>0.182765857541043</v>
+        <v>0.1047236571665728</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7285710881298009</v>
+        <v>0.5799863577819757</v>
       </c>
       <c r="K3" t="n">
         <v>0.1575694389017532</v>
@@ -577,27 +577,27 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.8813766183248144</v>
+        <v>0.646063827850067</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1214989855920932</v>
+        <v>-0.06202339389086625</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>y = 0.881x - 0.121</t>
+          <t>y = 0.646x - 0.062</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.8652161582416737</v>
+        <v>0.8587576421472526</v>
       </c>
       <c r="H4" t="n">
-        <v>0.07334387741481165</v>
+        <v>0.07359910614288688</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1378513827868724</v>
+        <v>0.09600196020455755</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7598776327327212</v>
+        <v>0.5840404339592007</v>
       </c>
       <c r="K4" t="n">
         <v>0.1575694389017532</v>
